--- a/VerveStacks_ZAF/SysSettings.xlsx
+++ b/VerveStacks_ZAF/SysSettings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70F2DFF4-BB03-4056-AB76-34270AF84765}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86312F6F-D97C-4956-884D-2E7A1D220904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="432">
   <si>
     <t>~BookRegions_Map</t>
   </si>
@@ -674,6 +674,27 @@
   </si>
   <si>
     <t>OIL</t>
+  </si>
+  <si>
+    <t>cap_bnd</t>
+  </si>
+  <si>
+    <t>~tfm_comgrp</t>
+  </si>
+  <si>
+    <t>allregions</t>
+  </si>
+  <si>
+    <t>cset_cn</t>
+  </si>
+  <si>
+    <t>ELC,e[_]*</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>ELC_BatIn</t>
   </si>
   <si>
     <t>ZAF</t>
@@ -3703,7 +3724,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
@@ -3786,7 +3807,7 @@
         <v>16</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>10</v>
@@ -3818,10 +3839,10 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="O5" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="P5" t="s">
         <v>25</v>
@@ -3830,7 +3851,7 @@
         <v>35</v>
       </c>
       <c r="R5" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="2:18">
@@ -3847,10 +3868,10 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="O6" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="P6" t="s">
         <v>25</v>
@@ -3859,7 +3880,7 @@
         <v>35</v>
       </c>
       <c r="R6" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="2:18">
@@ -3876,10 +3897,10 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="O7" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="P7" t="s">
         <v>25</v>
@@ -3888,7 +3909,7 @@
         <v>35</v>
       </c>
       <c r="R7" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="8" spans="2:18">
@@ -3905,10 +3926,10 @@
         <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="O8" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="P8" t="s">
         <v>25</v>
@@ -3917,7 +3938,7 @@
         <v>35</v>
       </c>
       <c r="R8" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="2:18">
@@ -3934,10 +3955,10 @@
         <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="O9" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
@@ -3946,7 +3967,7 @@
         <v>35</v>
       </c>
       <c r="R9" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="2:18">
@@ -3963,10 +3984,10 @@
         <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="O10" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
@@ -3975,7 +3996,7 @@
         <v>35</v>
       </c>
       <c r="R10" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="2:18">
@@ -3992,10 +4013,10 @@
         <v>17</v>
       </c>
       <c r="N11" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="O11" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="P11" t="s">
         <v>25</v>
@@ -4004,7 +4025,7 @@
         <v>35</v>
       </c>
       <c r="R11" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="2:18">
@@ -4021,10 +4042,10 @@
         <v>17</v>
       </c>
       <c r="N12" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="O12" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="P12" t="s">
         <v>25</v>
@@ -4033,7 +4054,7 @@
         <v>35</v>
       </c>
       <c r="R12" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="2:18">
@@ -4050,10 +4071,10 @@
         <v>17</v>
       </c>
       <c r="N13" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="O13" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="P13" t="s">
         <v>25</v>
@@ -4062,7 +4083,7 @@
         <v>35</v>
       </c>
       <c r="R13" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="2:18">
@@ -4082,10 +4103,10 @@
         <v>17</v>
       </c>
       <c r="N14" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="O14" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="P14" t="s">
         <v>25</v>
@@ -4094,7 +4115,7 @@
         <v>35</v>
       </c>
       <c r="R14" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="2:18">
@@ -4114,10 +4135,10 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="O15" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="P15" t="s">
         <v>25</v>
@@ -4126,7 +4147,7 @@
         <v>35</v>
       </c>
       <c r="R15" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="2:18">
@@ -4155,10 +4176,10 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="O16" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="P16" t="s">
         <v>25</v>
@@ -4167,7 +4188,7 @@
         <v>35</v>
       </c>
       <c r="R16" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" spans="2:18">
@@ -4187,10 +4208,10 @@
         <v>17</v>
       </c>
       <c r="N17" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="O17" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="P17" t="s">
         <v>25</v>
@@ -4199,7 +4220,7 @@
         <v>35</v>
       </c>
       <c r="R17" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="2:18">
@@ -4219,10 +4240,10 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="O18" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="P18" t="s">
         <v>25</v>
@@ -4231,7 +4252,7 @@
         <v>35</v>
       </c>
       <c r="R18" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="2:18">
@@ -4251,10 +4272,10 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="O19" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="P19" t="s">
         <v>25</v>
@@ -4263,7 +4284,7 @@
         <v>35</v>
       </c>
       <c r="R19" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="20" spans="2:18">
@@ -4283,10 +4304,10 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="O20" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="P20" t="s">
         <v>25</v>
@@ -4295,7 +4316,7 @@
         <v>35</v>
       </c>
       <c r="R20" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="21" spans="2:18">
@@ -4321,10 +4342,10 @@
         <v>17</v>
       </c>
       <c r="N21" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="O21" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="P21" t="s">
         <v>25</v>
@@ -4333,7 +4354,7 @@
         <v>35</v>
       </c>
       <c r="R21" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" spans="2:18">
@@ -4353,10 +4374,10 @@
         <v>17</v>
       </c>
       <c r="N22" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="O22" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="P22" t="s">
         <v>25</v>
@@ -4365,7 +4386,7 @@
         <v>35</v>
       </c>
       <c r="R22" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="2:18">
@@ -4382,10 +4403,10 @@
         <v>17</v>
       </c>
       <c r="N23" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="O23" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="P23" t="s">
         <v>25</v>
@@ -4394,7 +4415,7 @@
         <v>35</v>
       </c>
       <c r="R23" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="24" spans="2:18">
@@ -4411,10 +4432,10 @@
         <v>17</v>
       </c>
       <c r="N24" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="O24" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="P24" t="s">
         <v>25</v>
@@ -4423,7 +4444,7 @@
         <v>35</v>
       </c>
       <c r="R24" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="2:18">
@@ -4431,10 +4452,10 @@
         <v>17</v>
       </c>
       <c r="N25" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="O25" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s">
         <v>25</v>
@@ -4443,7 +4464,7 @@
         <v>35</v>
       </c>
       <c r="R25" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="2:18">
@@ -4451,10 +4472,10 @@
         <v>17</v>
       </c>
       <c r="N26" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="O26" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="P26" t="s">
         <v>25</v>
@@ -4463,7 +4484,7 @@
         <v>35</v>
       </c>
       <c r="R26" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="27" spans="2:18">
@@ -4471,10 +4492,10 @@
         <v>17</v>
       </c>
       <c r="N27" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="O27" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="P27" t="s">
         <v>25</v>
@@ -4483,58 +4504,81 @@
         <v>35</v>
       </c>
       <c r="R27" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" ht="17.649999999999999" thickBot="1">
+      <c r="B28" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="M28" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" t="s">
+        <v>268</v>
+      </c>
+      <c r="O28" t="s">
+        <v>269</v>
+      </c>
+      <c r="P28" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>35</v>
+      </c>
+      <c r="R28" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" ht="15" thickTop="1" thickBot="1">
+      <c r="B29" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="M29" t="s">
+        <v>17</v>
+      </c>
+      <c r="N29" t="s">
+        <v>270</v>
+      </c>
+      <c r="O29" t="s">
+        <v>271</v>
+      </c>
+      <c r="P29" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>35</v>
+      </c>
+      <c r="R29" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18">
+      <c r="B30" t="s">
+        <v>218</v>
+      </c>
+      <c r="C30" t="s">
+        <v>217</v>
+      </c>
+      <c r="D30" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="28" spans="2:18">
-      <c r="M28" t="s">
-        <v>17</v>
-      </c>
-      <c r="N28" t="s">
-        <v>261</v>
-      </c>
-      <c r="O28" t="s">
-        <v>262</v>
-      </c>
-      <c r="P28" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>35</v>
-      </c>
-      <c r="R28" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="29" spans="2:18">
-      <c r="M29" t="s">
-        <v>17</v>
-      </c>
-      <c r="N29" t="s">
-        <v>263</v>
-      </c>
-      <c r="O29" t="s">
-        <v>264</v>
-      </c>
-      <c r="P29" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>35</v>
-      </c>
-      <c r="R29" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="30" spans="2:18">
       <c r="M30" t="s">
         <v>17</v>
       </c>
       <c r="N30" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="O30" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="P30" t="s">
         <v>25</v>
@@ -4543,7 +4587,7 @@
         <v>35</v>
       </c>
       <c r="R30" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="2:18">
@@ -4551,10 +4595,10 @@
         <v>17</v>
       </c>
       <c r="N31" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="O31" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="P31" t="s">
         <v>25</v>
@@ -4563,7 +4607,7 @@
         <v>35</v>
       </c>
       <c r="R31" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="2:18">
@@ -4571,10 +4615,10 @@
         <v>17</v>
       </c>
       <c r="N32" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="O32" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="P32" t="s">
         <v>25</v>
@@ -4583,7 +4627,7 @@
         <v>35</v>
       </c>
       <c r="R32" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="33" spans="13:18">
@@ -4591,10 +4635,10 @@
         <v>17</v>
       </c>
       <c r="N33" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="O33" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="P33" t="s">
         <v>25</v>
@@ -4603,7 +4647,7 @@
         <v>35</v>
       </c>
       <c r="R33" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="34" spans="13:18">
@@ -4611,10 +4655,10 @@
         <v>17</v>
       </c>
       <c r="N34" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="O34" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="P34" t="s">
         <v>25</v>
@@ -4623,7 +4667,7 @@
         <v>35</v>
       </c>
       <c r="R34" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="13:18">
@@ -4631,10 +4675,10 @@
         <v>17</v>
       </c>
       <c r="N35" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="O35" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="P35" t="s">
         <v>25</v>
@@ -4643,7 +4687,7 @@
         <v>35</v>
       </c>
       <c r="R35" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="13:18">
@@ -4651,10 +4695,10 @@
         <v>17</v>
       </c>
       <c r="N36" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="O36" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="P36" t="s">
         <v>25</v>
@@ -4663,7 +4707,7 @@
         <v>35</v>
       </c>
       <c r="R36" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="13:18">
@@ -4671,10 +4715,10 @@
         <v>17</v>
       </c>
       <c r="N37" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="O37" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="P37" t="s">
         <v>25</v>
@@ -4683,7 +4727,7 @@
         <v>35</v>
       </c>
       <c r="R37" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38" spans="13:18">
@@ -4691,10 +4735,10 @@
         <v>17</v>
       </c>
       <c r="N38" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="O38" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="P38" t="s">
         <v>25</v>
@@ -4703,7 +4747,7 @@
         <v>35</v>
       </c>
       <c r="R38" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39" spans="13:18">
@@ -4711,10 +4755,10 @@
         <v>17</v>
       </c>
       <c r="N39" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="O39" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="P39" t="s">
         <v>25</v>
@@ -4723,7 +4767,7 @@
         <v>35</v>
       </c>
       <c r="R39" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="13:18">
@@ -4731,10 +4775,10 @@
         <v>17</v>
       </c>
       <c r="N40" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="O40" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="P40" t="s">
         <v>25</v>
@@ -4743,7 +4787,7 @@
         <v>35</v>
       </c>
       <c r="R40" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="13:18">
@@ -4751,10 +4795,10 @@
         <v>17</v>
       </c>
       <c r="N41" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="O41" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="P41" t="s">
         <v>25</v>
@@ -4763,7 +4807,7 @@
         <v>35</v>
       </c>
       <c r="R41" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" spans="13:18">
@@ -4771,10 +4815,10 @@
         <v>17</v>
       </c>
       <c r="N42" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="O42" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="P42" t="s">
         <v>25</v>
@@ -4783,7 +4827,7 @@
         <v>35</v>
       </c>
       <c r="R42" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="13:18">
@@ -4791,10 +4835,10 @@
         <v>17</v>
       </c>
       <c r="N43" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="O43" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="P43" t="s">
         <v>25</v>
@@ -4803,7 +4847,7 @@
         <v>35</v>
       </c>
       <c r="R43" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="44" spans="13:18">
@@ -4811,10 +4855,10 @@
         <v>17</v>
       </c>
       <c r="N44" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="O44" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="P44" t="s">
         <v>25</v>
@@ -4823,7 +4867,7 @@
         <v>35</v>
       </c>
       <c r="R44" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="45" spans="13:18">
@@ -4831,10 +4875,10 @@
         <v>17</v>
       </c>
       <c r="N45" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="O45" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="P45" t="s">
         <v>25</v>
@@ -4843,7 +4887,7 @@
         <v>35</v>
       </c>
       <c r="R45" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="13:18">
@@ -4851,10 +4895,10 @@
         <v>17</v>
       </c>
       <c r="N46" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="O46" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="P46" t="s">
         <v>25</v>
@@ -4863,7 +4907,7 @@
         <v>35</v>
       </c>
       <c r="R46" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="13:18">
@@ -4871,10 +4915,10 @@
         <v>17</v>
       </c>
       <c r="N47" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="O47" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="P47" t="s">
         <v>25</v>
@@ -4883,7 +4927,7 @@
         <v>35</v>
       </c>
       <c r="R47" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="48" spans="13:18">
@@ -4891,10 +4935,10 @@
         <v>17</v>
       </c>
       <c r="N48" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="O48" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="P48" t="s">
         <v>25</v>
@@ -4903,7 +4947,7 @@
         <v>35</v>
       </c>
       <c r="R48" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" spans="13:18">
@@ -4911,10 +4955,10 @@
         <v>17</v>
       </c>
       <c r="N49" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="O49" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="P49" t="s">
         <v>25</v>
@@ -4923,7 +4967,7 @@
         <v>35</v>
       </c>
       <c r="R49" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" spans="13:18">
@@ -4931,10 +4975,10 @@
         <v>17</v>
       </c>
       <c r="N50" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="O50" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="P50" t="s">
         <v>25</v>
@@ -4943,7 +4987,7 @@
         <v>35</v>
       </c>
       <c r="R50" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="51" spans="13:18">
@@ -4951,10 +4995,10 @@
         <v>17</v>
       </c>
       <c r="N51" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="O51" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="P51" t="s">
         <v>25</v>
@@ -4963,7 +5007,7 @@
         <v>35</v>
       </c>
       <c r="R51" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="52" spans="13:18">
@@ -4971,10 +5015,10 @@
         <v>17</v>
       </c>
       <c r="N52" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="O52" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="P52" t="s">
         <v>25</v>
@@ -4983,7 +5027,7 @@
         <v>35</v>
       </c>
       <c r="R52" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="53" spans="13:18">
@@ -4991,10 +5035,10 @@
         <v>17</v>
       </c>
       <c r="N53" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="O53" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="P53" t="s">
         <v>25</v>
@@ -5003,7 +5047,7 @@
         <v>35</v>
       </c>
       <c r="R53" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="54" spans="13:18">
@@ -5011,10 +5055,10 @@
         <v>17</v>
       </c>
       <c r="N54" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="O54" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="P54" t="s">
         <v>25</v>
@@ -5023,7 +5067,7 @@
         <v>35</v>
       </c>
       <c r="R54" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55" spans="13:18">
@@ -5031,10 +5075,10 @@
         <v>17</v>
       </c>
       <c r="N55" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="O55" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="P55" t="s">
         <v>25</v>
@@ -5043,7 +5087,7 @@
         <v>35</v>
       </c>
       <c r="R55" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="56" spans="13:18">
@@ -5051,10 +5095,10 @@
         <v>17</v>
       </c>
       <c r="N56" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="O56" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="P56" t="s">
         <v>25</v>
@@ -5063,7 +5107,7 @@
         <v>35</v>
       </c>
       <c r="R56" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="57" spans="13:18">
@@ -5071,10 +5115,10 @@
         <v>17</v>
       </c>
       <c r="N57" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="O57" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="P57" t="s">
         <v>25</v>
@@ -5083,7 +5127,7 @@
         <v>35</v>
       </c>
       <c r="R57" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="13:18">
@@ -5091,10 +5135,10 @@
         <v>17</v>
       </c>
       <c r="N58" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="O58" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="P58" t="s">
         <v>25</v>
@@ -5103,7 +5147,7 @@
         <v>35</v>
       </c>
       <c r="R58" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="59" spans="13:18">
@@ -5111,10 +5155,10 @@
         <v>17</v>
       </c>
       <c r="N59" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="O59" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="P59" t="s">
         <v>25</v>
@@ -5123,7 +5167,7 @@
         <v>35</v>
       </c>
       <c r="R59" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="60" spans="13:18">
@@ -5131,10 +5175,10 @@
         <v>17</v>
       </c>
       <c r="N60" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="O60" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="P60" t="s">
         <v>25</v>
@@ -5143,7 +5187,7 @@
         <v>35</v>
       </c>
       <c r="R60" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="13:18">
@@ -5151,10 +5195,10 @@
         <v>17</v>
       </c>
       <c r="N61" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="O61" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="P61" t="s">
         <v>25</v>
@@ -5163,7 +5207,7 @@
         <v>35</v>
       </c>
       <c r="R61" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="62" spans="13:18">
@@ -5171,10 +5215,10 @@
         <v>17</v>
       </c>
       <c r="N62" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="O62" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="P62" t="s">
         <v>25</v>
@@ -5183,7 +5227,7 @@
         <v>35</v>
       </c>
       <c r="R62" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="63" spans="13:18">
@@ -5191,10 +5235,10 @@
         <v>17</v>
       </c>
       <c r="N63" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="O63" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="P63" t="s">
         <v>25</v>
@@ -5203,7 +5247,7 @@
         <v>35</v>
       </c>
       <c r="R63" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="64" spans="13:18">
@@ -5211,10 +5255,10 @@
         <v>17</v>
       </c>
       <c r="N64" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="O64" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="P64" t="s">
         <v>25</v>
@@ -5223,7 +5267,7 @@
         <v>35</v>
       </c>
       <c r="R64" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="65" spans="13:18">
@@ -5231,10 +5275,10 @@
         <v>17</v>
       </c>
       <c r="N65" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="O65" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="P65" t="s">
         <v>25</v>
@@ -5243,7 +5287,7 @@
         <v>35</v>
       </c>
       <c r="R65" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="66" spans="13:18">
@@ -5251,10 +5295,10 @@
         <v>17</v>
       </c>
       <c r="N66" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="O66" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="P66" t="s">
         <v>25</v>
@@ -5263,7 +5307,7 @@
         <v>35</v>
       </c>
       <c r="R66" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="67" spans="13:18">
@@ -5271,10 +5315,10 @@
         <v>17</v>
       </c>
       <c r="N67" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="O67" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="P67" t="s">
         <v>25</v>
@@ -5283,7 +5327,7 @@
         <v>35</v>
       </c>
       <c r="R67" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="68" spans="13:18">
@@ -5291,10 +5335,10 @@
         <v>17</v>
       </c>
       <c r="N68" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="O68" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="P68" t="s">
         <v>25</v>
@@ -5303,7 +5347,7 @@
         <v>35</v>
       </c>
       <c r="R68" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="69" spans="13:18">
@@ -5311,10 +5355,10 @@
         <v>17</v>
       </c>
       <c r="N69" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="O69" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="P69" t="s">
         <v>25</v>
@@ -5323,7 +5367,7 @@
         <v>35</v>
       </c>
       <c r="R69" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="70" spans="13:18">
@@ -5331,10 +5375,10 @@
         <v>17</v>
       </c>
       <c r="N70" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="O70" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="P70" t="s">
         <v>25</v>
@@ -5343,7 +5387,7 @@
         <v>35</v>
       </c>
       <c r="R70" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="71" spans="13:18">
@@ -5351,10 +5395,10 @@
         <v>17</v>
       </c>
       <c r="N71" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="O71" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="P71" t="s">
         <v>25</v>
@@ -5363,7 +5407,7 @@
         <v>35</v>
       </c>
       <c r="R71" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="72" spans="13:18">
@@ -5371,10 +5415,10 @@
         <v>17</v>
       </c>
       <c r="N72" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="O72" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="P72" t="s">
         <v>25</v>
@@ -5383,7 +5427,7 @@
         <v>35</v>
       </c>
       <c r="R72" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="73" spans="13:18">
@@ -5391,10 +5435,10 @@
         <v>17</v>
       </c>
       <c r="N73" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="O73" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="P73" t="s">
         <v>25</v>
@@ -5403,7 +5447,7 @@
         <v>35</v>
       </c>
       <c r="R73" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="74" spans="13:18">
@@ -5411,10 +5455,10 @@
         <v>17</v>
       </c>
       <c r="N74" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="O74" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="P74" t="s">
         <v>25</v>
@@ -5423,7 +5467,7 @@
         <v>35</v>
       </c>
       <c r="R74" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="75" spans="13:18">
@@ -5431,10 +5475,10 @@
         <v>17</v>
       </c>
       <c r="N75" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="O75" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="P75" t="s">
         <v>25</v>
@@ -5443,7 +5487,7 @@
         <v>35</v>
       </c>
       <c r="R75" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="76" spans="13:18">
@@ -5451,10 +5495,10 @@
         <v>17</v>
       </c>
       <c r="N76" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="O76" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="P76" t="s">
         <v>25</v>
@@ -5463,7 +5507,7 @@
         <v>35</v>
       </c>
       <c r="R76" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="77" spans="13:18">
@@ -5471,10 +5515,10 @@
         <v>17</v>
       </c>
       <c r="N77" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="O77" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="P77" t="s">
         <v>25</v>
@@ -5483,7 +5527,7 @@
         <v>35</v>
       </c>
       <c r="R77" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="78" spans="13:18">
@@ -5491,10 +5535,10 @@
         <v>17</v>
       </c>
       <c r="N78" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="O78" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="P78" t="s">
         <v>25</v>
@@ -5503,7 +5547,7 @@
         <v>35</v>
       </c>
       <c r="R78" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="79" spans="13:18">
@@ -5511,10 +5555,10 @@
         <v>17</v>
       </c>
       <c r="N79" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="O79" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="P79" t="s">
         <v>25</v>
@@ -5523,7 +5567,7 @@
         <v>35</v>
       </c>
       <c r="R79" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="80" spans="13:18">
@@ -5531,10 +5575,10 @@
         <v>17</v>
       </c>
       <c r="N80" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="O80" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="P80" t="s">
         <v>25</v>
@@ -5543,7 +5587,7 @@
         <v>35</v>
       </c>
       <c r="R80" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="81" spans="13:18">
@@ -5551,10 +5595,10 @@
         <v>17</v>
       </c>
       <c r="N81" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="O81" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="P81" t="s">
         <v>25</v>
@@ -5563,7 +5607,7 @@
         <v>35</v>
       </c>
       <c r="R81" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="82" spans="13:18">
@@ -5571,10 +5615,10 @@
         <v>17</v>
       </c>
       <c r="N82" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="O82" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="P82" t="s">
         <v>25</v>
@@ -5583,7 +5627,7 @@
         <v>35</v>
       </c>
       <c r="R82" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="83" spans="13:18">
@@ -5591,10 +5635,10 @@
         <v>17</v>
       </c>
       <c r="N83" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="O83" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="P83" t="s">
         <v>25</v>
@@ -5603,7 +5647,7 @@
         <v>35</v>
       </c>
       <c r="R83" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="84" spans="13:18">
@@ -5611,10 +5655,10 @@
         <v>17</v>
       </c>
       <c r="N84" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="O84" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="P84" t="s">
         <v>25</v>
@@ -5623,7 +5667,7 @@
         <v>35</v>
       </c>
       <c r="R84" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="85" spans="13:18">
@@ -5631,10 +5675,10 @@
         <v>17</v>
       </c>
       <c r="N85" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="O85" t="s">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="P85" t="s">
         <v>25</v>
@@ -5643,7 +5687,7 @@
         <v>35</v>
       </c>
       <c r="R85" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="86" spans="13:18">
@@ -5651,10 +5695,10 @@
         <v>17</v>
       </c>
       <c r="N86" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="O86" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="P86" t="s">
         <v>25</v>
@@ -5663,7 +5707,7 @@
         <v>35</v>
       </c>
       <c r="R86" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="87" spans="13:18">
@@ -5671,10 +5715,10 @@
         <v>17</v>
       </c>
       <c r="N87" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="O87" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="P87" t="s">
         <v>25</v>
@@ -5683,7 +5727,7 @@
         <v>35</v>
       </c>
       <c r="R87" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="88" spans="13:18">
@@ -5691,10 +5735,10 @@
         <v>17</v>
       </c>
       <c r="N88" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="O88" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="P88" t="s">
         <v>25</v>
@@ -5703,7 +5747,7 @@
         <v>35</v>
       </c>
       <c r="R88" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="89" spans="13:18">
@@ -5711,10 +5755,10 @@
         <v>17</v>
       </c>
       <c r="N89" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="O89" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="P89" t="s">
         <v>25</v>
@@ -5723,7 +5767,7 @@
         <v>35</v>
       </c>
       <c r="R89" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="90" spans="13:18">
@@ -5731,10 +5775,10 @@
         <v>17</v>
       </c>
       <c r="N90" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="O90" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="P90" t="s">
         <v>25</v>
@@ -5743,7 +5787,7 @@
         <v>35</v>
       </c>
       <c r="R90" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="91" spans="13:18">
@@ -5751,10 +5795,10 @@
         <v>17</v>
       </c>
       <c r="N91" t="s">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="O91" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="P91" t="s">
         <v>25</v>
@@ -5763,7 +5807,7 @@
         <v>35</v>
       </c>
       <c r="R91" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="92" spans="13:18">
@@ -5771,10 +5815,10 @@
         <v>17</v>
       </c>
       <c r="N92" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="O92" t="s">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="P92" t="s">
         <v>25</v>
@@ -5783,7 +5827,7 @@
         <v>35</v>
       </c>
       <c r="R92" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="93" spans="13:18">
@@ -5791,10 +5835,10 @@
         <v>17</v>
       </c>
       <c r="N93" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="O93" t="s">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="P93" t="s">
         <v>25</v>
@@ -5803,7 +5847,7 @@
         <v>35</v>
       </c>
       <c r="R93" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="94" spans="13:18">
@@ -5811,10 +5855,10 @@
         <v>17</v>
       </c>
       <c r="N94" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="O94" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="P94" t="s">
         <v>25</v>
@@ -5823,7 +5867,7 @@
         <v>35</v>
       </c>
       <c r="R94" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="95" spans="13:18">
@@ -5831,10 +5875,10 @@
         <v>17</v>
       </c>
       <c r="N95" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="O95" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="P95" t="s">
         <v>25</v>
@@ -5843,7 +5887,7 @@
         <v>35</v>
       </c>
       <c r="R95" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="96" spans="13:18">
@@ -5851,10 +5895,10 @@
         <v>17</v>
       </c>
       <c r="N96" t="s">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="O96" t="s">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="P96" t="s">
         <v>25</v>
@@ -5863,7 +5907,7 @@
         <v>35</v>
       </c>
       <c r="R96" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="97" spans="13:18">
@@ -5871,10 +5915,10 @@
         <v>17</v>
       </c>
       <c r="N97" t="s">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="O97" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="P97" t="s">
         <v>25</v>
@@ -5883,7 +5927,7 @@
         <v>35</v>
       </c>
       <c r="R97" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="98" spans="13:18">
@@ -5891,10 +5935,10 @@
         <v>17</v>
       </c>
       <c r="N98" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="O98" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="P98" t="s">
         <v>25</v>
@@ -5903,7 +5947,7 @@
         <v>35</v>
       </c>
       <c r="R98" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99" spans="13:18">
@@ -5911,10 +5955,10 @@
         <v>17</v>
       </c>
       <c r="N99" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="O99" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="P99" t="s">
         <v>25</v>
@@ -5923,7 +5967,7 @@
         <v>35</v>
       </c>
       <c r="R99" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="100" spans="13:18">
@@ -5931,10 +5975,10 @@
         <v>17</v>
       </c>
       <c r="N100" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="O100" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="P100" t="s">
         <v>25</v>
@@ -5943,7 +5987,7 @@
         <v>35</v>
       </c>
       <c r="R100" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="101" spans="13:18">
@@ -5951,10 +5995,10 @@
         <v>17</v>
       </c>
       <c r="N101" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="O101" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="P101" t="s">
         <v>25</v>
@@ -5963,7 +6007,7 @@
         <v>35</v>
       </c>
       <c r="R101" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="102" spans="13:18">
@@ -5971,10 +6015,10 @@
         <v>17</v>
       </c>
       <c r="N102" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="O102" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="P102" t="s">
         <v>25</v>
@@ -5983,7 +6027,7 @@
         <v>35</v>
       </c>
       <c r="R102" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="103" spans="13:18">
@@ -5991,10 +6035,10 @@
         <v>17</v>
       </c>
       <c r="N103" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="O103" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="P103" t="s">
         <v>25</v>
@@ -6003,7 +6047,7 @@
         <v>35</v>
       </c>
       <c r="R103" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="104" spans="13:18">
@@ -6011,10 +6055,10 @@
         <v>17</v>
       </c>
       <c r="N104" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="O104" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="P104" t="s">
         <v>25</v>
@@ -6023,7 +6067,7 @@
         <v>35</v>
       </c>
       <c r="R104" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="105" spans="13:18">
@@ -6031,10 +6075,10 @@
         <v>17</v>
       </c>
       <c r="N105" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="O105" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="P105" t="s">
         <v>25</v>
@@ -6043,7 +6087,7 @@
         <v>35</v>
       </c>
       <c r="R105" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="106" spans="13:18">
@@ -6051,10 +6095,10 @@
         <v>17</v>
       </c>
       <c r="N106" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="O106" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="P106" t="s">
         <v>25</v>
@@ -6063,7 +6107,7 @@
         <v>35</v>
       </c>
       <c r="R106" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="107" spans="13:18">
@@ -6071,10 +6115,10 @@
         <v>17</v>
       </c>
       <c r="N107" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="O107" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="P107" t="s">
         <v>25</v>
@@ -6083,7 +6127,7 @@
         <v>35</v>
       </c>
       <c r="R107" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="108" spans="13:18">
@@ -6091,10 +6135,10 @@
         <v>17</v>
       </c>
       <c r="N108" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="O108" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="P108" t="s">
         <v>25</v>
@@ -6103,7 +6147,7 @@
         <v>35</v>
       </c>
       <c r="R108" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="109" spans="13:18">
@@ -6111,10 +6155,10 @@
         <v>17</v>
       </c>
       <c r="N109" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="O109" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="P109" t="s">
         <v>25</v>
@@ -6123,7 +6167,7 @@
         <v>35</v>
       </c>
       <c r="R109" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -6414,7 +6458,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A64C410-895F-4040-A7AB-3F7211AA7FBD}">
-  <dimension ref="B1:N41"/>
+  <dimension ref="B1:N42"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="11.3984375" style="11"/>
@@ -6556,49 +6600,49 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="2:12">
-      <c r="B13" s="14" t="s">
+    <row r="11" spans="2:12">
+      <c r="D11" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="E11" s="11">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-    </row>
-    <row r="14" spans="2:12">
-      <c r="B14" s="15" t="s">
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D15" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E15" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F15" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G15" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H15" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I15" s="15" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12">
-      <c r="D15" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="F15" s="11">
-        <v>2222</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -6606,22 +6650,22 @@
         <v>66</v>
       </c>
       <c r="F16" s="11">
+        <v>2222</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="D17" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="11">
         <v>8888</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G17" s="11" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="17" spans="2:14" ht="12.75">
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
     </row>
     <row r="18" spans="2:14" ht="12.75">
       <c r="B18" s="13"/>
@@ -6645,20 +6689,16 @@
       <c r="I19" s="13"/>
       <c r="J19" s="13"/>
     </row>
-    <row r="20" spans="2:14" ht="14.25">
-      <c r="B20"/>
-      <c r="C20"/>
-      <c r="D20"/>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20"/>
-      <c r="H20"/>
-      <c r="I20"/>
-      <c r="J20"/>
-      <c r="K20"/>
-      <c r="L20"/>
-      <c r="M20"/>
-      <c r="N20"/>
+    <row r="20" spans="2:14" ht="12.75">
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
     </row>
     <row r="21" spans="2:14" ht="14.25">
       <c r="B21"/>
@@ -6974,6 +7014,21 @@
       <c r="L41"/>
       <c r="M41"/>
       <c r="N41"/>
+    </row>
+    <row r="42" spans="2:14" ht="14.25">
+      <c r="B42"/>
+      <c r="C42"/>
+      <c r="D42"/>
+      <c r="E42"/>
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="I42"/>
+      <c r="J42"/>
+      <c r="K42"/>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
